--- a/produits/preuves/sortie/c7-tontine/c7-tontine.xlsx
+++ b/produits/preuves/sortie/c7-tontine/c7-tontine.xlsx
@@ -268,6 +268,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="7.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.87"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -385,6 +386,9 @@
   </sheetPr>
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="5.87"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
